--- a/Fase 2/Evidencias Proyecto/PlanPruebas_MediTriage.xlsx
+++ b/Fase 2/Evidencias Proyecto/PlanPruebas_MediTriage.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\new-repo\MediTriage\Fase 2\Evidencias Proyecto\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAD2682-80BD-4383-964F-0D42EEC98AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -226,8 +232,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,9 +273,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -279,24 +283,138 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A153ED0-6150-48C9-B78E-AABF63D80C9E}" name="Tabla1" displayName="Tabla1" ref="A1:K9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="13" tableBorderDxfId="14">
+  <autoFilter ref="A1:K9" xr:uid="{4A153ED0-6150-48C9-B78E-AABF63D80C9E}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{96B46AC5-9C4B-43C3-9FC3-2D7C2D1D662B}" name="ID Prueba" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{5DF3A585-C964-48AC-8F4E-996CAC8F0198}" name="Nombre caso" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{8DFDACF5-01DB-4D7C-982C-28B85A119C53}" name="Módulo" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{3C8F8846-84AB-447F-A933-6B4E7337B9C7}" name="Requisito asociado" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{53BA729F-EE55-4789-8953-C8CFDB2BFE3F}" name="Precondiciones" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{ECF4CB21-BFCD-4720-B893-87AC271175D8}" name="Pasos" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{20E8223C-FD5E-429E-892C-EFEAE4EAA38F}" name="Datos de prueba" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{A03B2317-E083-4191-88E1-585679563B63}" name="Resultado esperado" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{BDD441E9-4696-4C1B-9651-C5519D0395DF}" name="Resultado obtenido" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{8116C5C0-C7ED-4F17-BC61-3C19C83ED68F}" name="Estado" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{6C29F7F5-4882-4A4E-B144-3DE02C722BF4}" name="Observaciones" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -334,7 +452,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -368,6 +486,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -402,9 +521,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -577,11 +697,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.85546875" customWidth="1"/>
+    <col min="6" max="6" width="66.28515625" customWidth="1"/>
+    <col min="7" max="7" width="71.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.85546875" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,215 +749,242 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>65</v>
       </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
         <v>67</v>
       </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>